--- a/TFT_prediction_remedy_plan/Iteration_3/Feature_engineering_set_up.xlsx
+++ b/TFT_prediction_remedy_plan/Iteration_3/Feature_engineering_set_up.xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\G0004878\Desktop\TFT_Data\Temporal-Fusion-Transformers-Material\TFT_prediction_remedy_plan\Iteration_3\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,133 +24,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t xml:space="preserve">Name of new feature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rationale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FESTIVE_DAYS_FROM_DIWALI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This will be a continuous feature to capture the momentum right after Dussehra and post-Diwali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Any CAL_DATE that lies within 20 days before Diwali and 10 days after Diwali will have value : DATEDIFF('day', CAL_DATE,DIWALI_DATE)
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>Name of new feature</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Rationale</t>
+  </si>
+  <si>
+    <t>FESTIVE_DAYS_FROM_DIWALI</t>
+  </si>
+  <si>
+    <t>This will be a continuous feature to capture the momentum right after Dussehra and post-Diwali</t>
+  </si>
+  <si>
+    <t>1. Any CAL_DATE that lies within 20 days before Diwali and 10 days after Diwali will have value : DATEDIFF('day', CAL_DATE,DIWALI_DATE)
 2. Any CAL_DATE outside this range will be clipped at -20 or +10</t>
   </si>
   <si>
-    <t xml:space="preserve">Reason for -20 is : To pick-up the momentum of sales after Dussehra which falls precisely 20 days before Diwali
+    <t>Reason for -20 is : To pick-up the momentum of sales after Dussehra which falls precisely 20 days before Diwali
 Reason for +10 is : Historically sales have started returning to their usual daily sales within 10 days after Diwali</t>
   </si>
   <si>
-    <t xml:space="preserve">IS_NAVRATARI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This will be a binary flag to indicate if it is navratari or not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 : If it is not Navratari
+    <t>IS_NAVRATARI</t>
+  </si>
+  <si>
+    <t>This will be a binary flag to indicate if it is navratari or not</t>
+  </si>
+  <si>
+    <t>0 : If it is not Navratari
 1 : If it is Navratari</t>
   </si>
   <si>
-    <t xml:space="preserve">Replaces the old NAVRATARI2..NAVRATARI8 block (7 separate one-hot day-offset flags). Tested against actual sales with the same &gt;2.5x-neighbor-spike rule used to justify Dhanteras: none of Navratri days 2-8 show a spike distinguishable from their immediate neighbors (min ratios 0.49x-0.80x across 2023-2025 - all well under the 2.5x bar). They were riding a flat, elevated plateau, not individually informative. Feeding 7 near-duplicate low-signal columns into TFT's variable selection network dilutes the attention weight available to genuinely informative covariates; one IS_NAVRATARI flag (ongoing, non-start/non-end days) gives the model one denser, better-supported signal instead of seven weak, mutually-correlated ones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IS_NAVRATARI_START</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary flag marking the first day of Navratri (Ghatasthapana), the day the festive period begins immediately after Pitru Paksha ends.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 : If it is not Navratari start
+    <t>IS_NAVRATARI_START</t>
+  </si>
+  <si>
+    <t>0 : If it is not Navratari start
 1 : If it is Navratari start</t>
   </si>
   <si>
-    <t xml:space="preserve">This flag will indicate if it is the beginning of the navratari season. There is always a huge peak of sales at NAVRATARI start so this feature will help the model learn that pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IS_NAVRATARI_END</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary flag marking the final day of the 9-night Navratri period (Maha Navami / Ashtami-Navami), the day before Dussehra.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 : If it is not Navratri's last day (Maha Navami)
+    <t>This flag will indicate if it is the beginning of the navratari season. There is always a huge peak of sales at NAVRATARI start so this feature will help the model learn that pattern</t>
+  </si>
+  <si>
+    <t>IS_NAVRATARI_END</t>
+  </si>
+  <si>
+    <t>Binary flag marking the final day of the 9-night Navratri period (Maha Navami / Ashtami-Navami), the day before Dussehra.</t>
+  </si>
+  <si>
+    <t>0 : If it is not Navratri's last day (Maha Navami)
 1 : If it is Maha Navami (Navratri day 9)</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT YET VALIDATED against actual sales. Tested with the same &gt;2.5x-neighbor-spike rule used to justify Dhanteras: Navratri day 9 shows ratios of 0.54x / 0.44x / 0.82x across 2023-2025 - it is LOWER than its immediate neighbors in all three years, not a spike. Current data does not support this as a standalone flag. Recommend re-testing on actual sales before finalizing, or dropping it and letting IS_NAVRATARI + the continuous axis cover this day.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IS_DUSSEHRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary flag marking Vijayadashami / Dussehra, the 10th and final day of the Navratri festival period.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 : If it is not Dussehra
+    <t>IS_DUSSEHRA</t>
+  </si>
+  <si>
+    <t>Binary flag marking Vijayadashami / Dussehra, the 10th and final day of the Navratri festival period.</t>
+  </si>
+  <si>
+    <t>0 : If it is not Dussehra
 1 : If it is Dussehra</t>
   </si>
   <si>
-    <t xml:space="preserve">Tested with the same &gt;2.5x-neighbor-spike rule: Dussehra shows ratios of 4.44x / 5.69x / 0.50x across 2023-2025 - it fails in 2025, where Dussehra day sales were actually BELOW its immediate neighbors. Inconsistent evidence across years (passes 2 of 3, fails the year that matters for the all-3-years bar). Recommend re-checking before including as a standalone flag rather than assuming it clears the bar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IS_PITRA_PAKSHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary suppression flag marking the 16-day Pitru Paksha period immediately preceding Navratri, when large discretionary purchases are traditionally avoided.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 : Outside Pitru Paksha
+    <t>IS_PITRA_PAKSHA</t>
+  </si>
+  <si>
+    <t>Binary suppression flag marking the 16-day Pitru Paksha period immediately preceding Navratri, when large discretionary purchases are traditionally avoided.</t>
+  </si>
+  <si>
+    <t>0 : Outside Pitru Paksha
 1 : Any CAL_DATE within the 16 days immediately before Navratri start (N-16 to N-1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmed suppression effect in actual sales: average daily sales during Pitru Paksha run at 44-53% of the pre-Pitru-Paksha baseline in all 3 years (2023: 53%, 2024: 49%, 2025: 44%). This is a demand-suppression pattern, not a spike, so the &gt;2.5x spike test used for the other flags doesn't apply here - the relevant evidence is the consistent ~2x drop versus baseline, holding in all 3 years.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IS_DHANTERAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary flag marking Dhanteras (2 days before Diwali) - the single largest sales day in the festive calendar, driven by the auspiciousness of buying gold/vehicles that day.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 : If it is not Dhanteras
+    <t>IS_DHANTERAS</t>
+  </si>
+  <si>
+    <t>Binary flag marking Dhanteras (2 days before Diwali) - the single largest sales day in the festive calendar, driven by the auspiciousness of buying gold/vehicles that day.</t>
+  </si>
+  <si>
+    <t>0 : If it is not Dhanteras
 1 : If it is Dhanteras (D-2)</t>
   </si>
   <si>
-    <t xml:space="preserve">Strongest empirical evidence of any candidate flag: sales on Dhanteras are 6.24x / 6.87x / 3.15x the average of its immediate neighbors, clearing the &gt;2.5x bar in all 3 years. Also the single highest-volume day in the entire festive window - higher than Diwali day itself every year (e.g. 2025: Dhanteras 42,306 vs Diwali day 9,655).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IS_DIWALI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary flag marking Diwali day itself - the anchor date (day 0) for FESTIVE_DAYS_FROM_DIWALI.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 : If it is not Diwali
-1 : If it is Diwali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caution: Diwali day itself is NOT the peak. Actual sales on Diwali day are lower than the days immediately around it - Dhanteras (D-2) runs 5-8x higher, and D+2/D+3 (Bhai Dooj, Govardhan Puja) meet or exceed Diwali day in multiple years. Tested with the same &gt;2.5x rule, Diwali day fails outright (ratios 0.83x / 0.76x / 0.73x - below its own neighbors, not above). Its real value is as the zero-point anchor for the continuous axis, not as a peak-detection flag; the actual peak is already covered by IS_DHANTERAS.</t>
+    <t>Replaces the old N to N+9 block (9 separate one-hot day-offset flags).  9 near-duplicate low-signal columns into TFT's variable selection network dilutes the attention weight available to genuinely informative covariates; one IS_NAVRATARI flag (ongoing, non-start/non-end days) gives the model one denser, better-supported signal instead of seven weak, mutually-correlated ones.</t>
+  </si>
+  <si>
+    <t>Since NAVRATARI_END shows peak greater than the usual NAVRATARI days hence I have kept it separate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same logic as NAVRATRI_END. </t>
+  </si>
+  <si>
+    <t>To capture the sales suppression effect</t>
+  </si>
+  <si>
+    <t>Boss of all the peaks! Have to capture it separately</t>
+  </si>
+  <si>
+    <t>Binary flag marking the first day of Navratri the day the festive period begins immediately after Pitru Paksha ends.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,22 +143,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -178,7 +151,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -201,80 +174,54 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -333,60 +280,76 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -418,7 +381,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -442,7 +405,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -502,165 +465,146 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="39.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34.09"/>
+    <col min="1" max="3" width="8.6328125" style="4"/>
+    <col min="4" max="4" width="26.36328125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="38.1796875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="39.6328125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="34.08984375" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="8.6328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D3" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="3"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="3" customFormat="true" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D4" s="4" t="s">
+    <row r="4" spans="1:7" s="1" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="D4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D5" s="4" t="s">
+    <row r="5" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="72.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="G6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="D7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="E7" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D7" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="G7" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="F8" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D8" s="4" t="s">
+      <c r="G8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="D9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D10" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D9" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>35</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>